--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_144_Sri_Lanka.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_144_Sri_Lanka.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rdd0d574911904ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8e964b2d78f94fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra1df881a2e7248fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R00ae625c5df34b23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8a0eb822dc99451e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0738fd5f1de34380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R99a3f8d1c8fb4286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6f1d251a7fd84790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R081b4b316ff34a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9c8e6b5977184d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rdd8a40d0ee394de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rebe43f72d79e4527"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ144CommercialTable" displayName="EEZ144CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ144CommercialTable" displayName="EEZ144CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ144FunctionalTable" displayName="EEZ144FunctionalTable" ref="A1:O15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O15"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ144FunctionalTable" displayName="EEZ144FunctionalTable" ref="A1:E15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E15"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ144ValidationTable" displayName="EEZ144ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ144ValidationTable" displayName="EEZ144ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5987,7 +5941,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R071ef43319d34256"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R719d557595a54824"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5997,20 +5951,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6018,444 +5962,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>35714.415130705</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.8353007883682175</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>68.43854822730461</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>35714.415130705</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>123.81236975276909</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$80,A2,'Species'!$U$2:$U$80))</x:f>
-        <x:v>4421886.371666738</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.8353007883682175</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>68.43854822730461</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2444242.7223327314</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1977643.6493340065</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.8091028076976687</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.8091028076976688</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>18601.5931037664</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.9071004231897066</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>80.74217111603944</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>18601.5931037664</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>96.6311887119006</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$80,A3,'Species'!$U$2:$U$80))</x:f>
-        <x:v>1797494.0535520401</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.9071004231897066</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>80.74217111603944</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1501933.013415246</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>295561.0401367941</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1967870986900526</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1967870986900526</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1590</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1590</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$80,A4,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20016.91404752726</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>20016.91404752726</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>165782.6439062556</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2740536774242504</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>187.95491087723562</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>165782.6439062556</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>208.51513679550686</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$80,A5,'Species'!$U$2:$U$80))</x:f>
-        <x:v>34568190.67243369</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2740536774242504</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>187.95491087723562</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>31159662.06039276</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3408528.6120409295</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1093891392478716</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.10938913924787173</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>77820.51613914469</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.6733529558086357</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>471.3602503310048</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>77820.51613914469</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>761.3027447255874</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$80,A6,'Species'!$U$2:$U$80))</x:f>
-        <x:v>59244972.53269272</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.6733529558086357</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>471.3602503310048</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>36681497.96823524</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>22563474.564457484</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.6151186787408895</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.6151186787408895</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5918.993790298701</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.793615936301537</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>621.7502038065802</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5918.993790298701</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>928.2901892583931</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$80,A7,'Species'!$U$2:$U$80))</x:f>
-        <x:v>5494543.865815635</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.793615936301537</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>621.7502038065802</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3680135.5954481</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1814408.2703675348</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.4930275592594324</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.4930275592594324</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>7293.619994689299</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.3963644012955525</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2490.946507686046</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>7293.619994689299</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2530.0396901212903</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$80,A8,'Species'!$U$2:$U$80))</x:f>
-        <x:v>18453148.07122616</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.3963644012955525</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2490.946507686046</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>18168017.254160427</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>285130.8170657344</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0156941075669905</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.01569410756699057</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f8d061b30c745ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R386f7d173e224028"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6465,20 +6120,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6486,822 +6131,288 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>11283.4081705907</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7989353971808986</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>629.4125485810215</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>11283.4081705907</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>632.3343363671071</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$80,A2,'Species'!$U$2:$U$80))</x:f>
-        <x:v>7134886.417509664</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7989353971808986</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>629.4125485810215</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7101918.693331413</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>32967.72417825088</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0046420869629509</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.004642086962950877</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>4388.438560093499</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.433519756065565</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2713.4370836560383</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>4388.438560093499</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2776.935758778408</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$80,A3,'Species'!$U$2:$U$80))</x:f>
-        <x:v>12186411.962725665</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.433519756065565</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2713.4370836560383</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>11907751.928303808</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>278660.03442185745</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0234015653080162</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.023401565308016205</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3116.8701974628</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.4632056752315923</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>290.53982809388395</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3116.8701974628</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>313.86463820405254</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$80,A4,'Species'!$U$2:$U$80))</x:f>
-        <x:v>978275.3368556555</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.4632056752315923</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>290.53982809388395</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>905574.9313617921</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>72700.40549386339</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0802809386347936</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08028093863479352</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4280.4490235439</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.403333333333334</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2531.2400495953684</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4280.4490235439</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2637.386666706511</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$80,A5,'Species'!$U$2:$U$80))</x:f>
-        <x:v>11289199.182211585</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.403333333333334</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2531.2400495953684</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>10834843.998645708</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>454355.1835658774</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0419346308652593</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04193463086525926</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2802.1235928359</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.1611393026147825</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1449.2366305254204</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2802.1235928359</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1611.7306675931704</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$80,A6,'Species'!$U$2:$U$80))</x:f>
-        <x:v>4516268.528959978</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.1611393026147825</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1449.2366305254204</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4060940.153997285</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>455328.37496269355</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.112123882080484</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.11212388208048386</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5525.131924283901</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2542043384898283</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>179.55782598246182</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5525.131924283901</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>223.69689963438768</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$80,A7,'Species'!$U$2:$U$80))</x:f>
-        <x:v>1235954.881533287</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2542043384898283</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>179.55782598246182</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>992080.6765907131</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>243874.2049425739</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2458209404709384</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.24582094047093833</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>61351.3073600628</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3367815347271708</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>217.16085092342658</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>61351.3073600628</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>233.27656643122938</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$80,A8,'Species'!$U$2:$U$80))</x:f>
-        <x:v>14311822.327022461</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3367815347271708</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>217.16085092342658</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>13323102.111575922</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>988720.2154465392</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0742109613186466</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.07421096131864657</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>41470.8509156468</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9144698406767144</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>821.2395203617922</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>41470.8509156468</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1070.0085985408057</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$80,A9,'Species'!$U$2:$U$80))</x:f>
-        <x:v>44374167.06854592</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9144698406767144</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>821.2395203617922</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>34057501.71496117</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>10316665.353584751</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.302919029115184</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.302919029115184</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5582.7342158296</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.6354628552562844</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>431.9792193163141</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5582.7342158296</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>452.1611904147091</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$80,A10,'Species'!$U$2:$U$80))</x:f>
-        <x:v>2524295.7487984393</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.6354628552562844</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>431.9792193163141</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2411625.1682045455</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>112670.58059389377</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.046719773072271</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04671977307227101</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5870.4490235441</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.3406201249860734</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>21.908877394394906</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5870.4490235441</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>23.03515263282666</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$80,A11,'Species'!$U$2:$U$80))</x:f>
-        <x:v>135226.68928056656</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.3406201249860734</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>21.908877394394906</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>128614.94790687299</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>6611.7413736935705</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.051407254609946</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.05140725460994607</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>30189.283206421096</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.7586345965230104</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>57.36336195011612</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>30189.283206421096</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>105.5318693176465</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$80,A12,'Species'!$U$2:$U$80))</x:f>
-        <x:v>3185931.4901334513</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.7586345965230104</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>57.36336195011612</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1731758.7795844956</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1454172.7105489557</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.8397085827957276</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.8397085827957277</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>24326.0726823969</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>24326.0726823969</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$80,A13,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4227386.926768689</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>4227386.926768689</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>111107.84685096641</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.184266200383243</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>152.85026653950553</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>111107.84685096641</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>160.86387237946013</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$80,A14,'Species'!$U$2:$U$80))</x:f>
-        <x:v>17873238.496190462</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.184266200383243</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>152.85026653950553</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>16982864.005800776</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>890374.4903896861</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.052427817244816</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.052427817244815954</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1426.8163411813</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.28</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>19.054607179632463</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1426.8163411813</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>19.054607179632463</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$80,A15,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>27187.424898690122</x:v>
       </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.28</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>19.054607179632463</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>27187.424898690122</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G15">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O15">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ce7b9b947f24dd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43656233baa146b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7476,7 +6587,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7575,7 +6686,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>124000252.48143452</x:v>
+        <x:v>93655505.52803203</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7589,7 +6700,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>124000252.48143451</x:v>
+        <x:v>108693151.46193188</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7603,7 +6714,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-30344746.95340249</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7617,7 +6728,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-15307101.01950264</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7628,9 +6739,9 @@
         <x:v>EEZ_144</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7642,47 +6753,19 @@
         <x:v>EEZ_144</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_144</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_144</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32d9fc4b96cb4905"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b678638b4944d34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7729,7 +6812,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
